--- a/selenium_auto/params.xlsx
+++ b/selenium_auto/params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurba\PycharmProjects\job\selenium_auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agdy\PycharmProjects\job\selenium_auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E30ABF-37D5-449E-988B-B86E4E4245A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8EBBA-578A-4B21-9281-9ED2B1053115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="28800" windowHeight="15370" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="25">
   <si>
     <t>Iot Id</t>
   </si>
@@ -109,12 +107,15 @@
   <si>
     <t>voltage</t>
   </si>
+  <si>
+    <t>NavTel</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,7 +184,7 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -522,30 +523,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C7F20B-1701-4DFE-B39C-A4574E6F742B}">
-  <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R45"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" customWidth="1"/>
-    <col min="2" max="2" width="17.36328125" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.90625" customWidth="1"/>
+    <col min="10" max="10" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.4140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.9140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -601,12 +602,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
-        <v>7385</v>
+        <v>11463</v>
       </c>
       <c r="B2" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -615,7 +616,7 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -657,12 +658,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
-        <v>7388</v>
+        <v>11346</v>
       </c>
       <c r="B3" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -671,7 +672,7 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -713,12 +714,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
-        <v>7391</v>
+        <v>11345</v>
       </c>
       <c r="B4" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -727,7 +728,7 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -769,12 +770,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
-        <v>7394</v>
+        <v>10423</v>
       </c>
       <c r="B5" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -783,7 +784,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -825,12 +826,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
-        <v>7397</v>
+        <v>10419</v>
       </c>
       <c r="B6" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -839,7 +840,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
@@ -881,12 +882,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
-        <v>7400</v>
+        <v>10418</v>
       </c>
       <c r="B7" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -895,7 +896,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -937,12 +938,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
-        <v>7403</v>
+        <v>10416</v>
       </c>
       <c r="B8" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -951,7 +952,7 @@
         <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
@@ -993,12 +994,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
-        <v>7406</v>
+        <v>10415</v>
       </c>
       <c r="B9" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1007,7 +1008,7 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -1049,12 +1050,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
-        <v>7409</v>
+        <v>10409</v>
       </c>
       <c r="B10" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1063,7 +1064,7 @@
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -1105,12 +1106,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
-        <v>7412</v>
+        <v>10408</v>
       </c>
       <c r="B11" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1119,7 +1120,7 @@
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -1161,12 +1162,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
-        <v>7415</v>
+        <v>10407</v>
       </c>
       <c r="B12" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1175,7 +1176,7 @@
         <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
@@ -1217,12 +1218,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
-        <v>7418</v>
+        <v>10379</v>
       </c>
       <c r="B13" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1231,7 +1232,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -1273,12 +1274,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
-        <v>7421</v>
+        <v>10378</v>
       </c>
       <c r="B14" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1287,7 +1288,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
@@ -1329,12 +1330,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
-        <v>7424</v>
+        <v>10377</v>
       </c>
       <c r="B15" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1343,7 +1344,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
@@ -1385,12 +1386,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
-        <v>7427</v>
+        <v>10376</v>
       </c>
       <c r="B16" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1399,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -1441,12 +1442,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18">
       <c r="A17" s="2">
-        <v>7430</v>
+        <v>10371</v>
       </c>
       <c r="B17" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1455,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1497,12 +1498,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18">
       <c r="A18" s="2">
-        <v>7433</v>
+        <v>10365</v>
       </c>
       <c r="B18" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1511,7 +1512,7 @@
         <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
@@ -1553,12 +1554,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18">
       <c r="A19" s="2">
-        <v>7436</v>
+        <v>10364</v>
       </c>
       <c r="B19" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1567,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
@@ -1609,12 +1610,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18">
       <c r="A20" s="2">
-        <v>7439</v>
+        <v>10363</v>
       </c>
       <c r="B20" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1623,7 +1624,7 @@
         <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
@@ -1665,12 +1666,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18">
       <c r="A21" s="2">
-        <v>7442</v>
+        <v>10362</v>
       </c>
       <c r="B21" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1679,7 +1680,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
@@ -1721,12 +1722,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18">
       <c r="A22" s="2">
-        <v>7445</v>
+        <v>10359</v>
       </c>
       <c r="B22" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1735,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
@@ -1777,12 +1778,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18">
       <c r="A23" s="2">
-        <v>7448</v>
+        <v>10180</v>
       </c>
       <c r="B23" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1791,7 +1792,7 @@
         <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
@@ -1833,12 +1834,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18">
       <c r="A24" s="2">
-        <v>7451</v>
+        <v>10179</v>
       </c>
       <c r="B24" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1847,7 +1848,7 @@
         <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
@@ -1889,12 +1890,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18">
       <c r="A25" s="2">
-        <v>7454</v>
+        <v>10178</v>
       </c>
       <c r="B25" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1903,7 +1904,7 @@
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -1945,12 +1946,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18">
       <c r="A26" s="2">
-        <v>7457</v>
+        <v>10177</v>
       </c>
       <c r="B26" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1959,7 +1960,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
@@ -2001,12 +2002,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18">
       <c r="A27" s="2">
-        <v>7460</v>
+        <v>10176</v>
       </c>
       <c r="B27" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2015,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
@@ -2057,12 +2058,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18">
       <c r="A28" s="2">
-        <v>7463</v>
+        <v>10175</v>
       </c>
       <c r="B28" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2071,7 +2072,7 @@
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
         <v>22</v>
@@ -2113,12 +2114,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18">
       <c r="A29" s="2">
-        <v>7466</v>
+        <v>10174</v>
       </c>
       <c r="B29" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2127,7 +2128,7 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
@@ -2169,12 +2170,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18">
       <c r="A30" s="2">
-        <v>7469</v>
+        <v>10173</v>
       </c>
       <c r="B30" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2183,7 +2184,7 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
         <v>22</v>
@@ -2225,12 +2226,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18">
       <c r="A31" s="2">
-        <v>7472</v>
+        <v>10172</v>
       </c>
       <c r="B31" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2239,7 +2240,7 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s">
         <v>22</v>
@@ -2281,12 +2282,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18">
       <c r="A32" s="2">
-        <v>7475</v>
+        <v>10171</v>
       </c>
       <c r="B32" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2295,7 +2296,7 @@
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
         <v>22</v>
@@ -2337,12 +2338,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18">
       <c r="A33" s="2">
-        <v>7478</v>
+        <v>10170</v>
       </c>
       <c r="B33" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2351,7 +2352,7 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -2393,12 +2394,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18">
       <c r="A34" s="2">
-        <v>7481</v>
+        <v>10169</v>
       </c>
       <c r="B34" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2407,7 +2408,7 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
@@ -2449,12 +2450,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18">
       <c r="A35" s="2">
-        <v>7484</v>
+        <v>10168</v>
       </c>
       <c r="B35" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2463,7 +2464,7 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
@@ -2505,12 +2506,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18">
       <c r="A36" s="2">
-        <v>7487</v>
+        <v>10167</v>
       </c>
       <c r="B36" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2519,7 +2520,7 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
         <v>22</v>
@@ -2561,12 +2562,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18">
       <c r="A37" s="2">
-        <v>7490</v>
+        <v>10166</v>
       </c>
       <c r="B37" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2575,7 +2576,7 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
         <v>22</v>
@@ -2617,12 +2618,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18">
       <c r="A38" s="2">
-        <v>7493</v>
+        <v>10165</v>
       </c>
       <c r="B38" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2631,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
         <v>22</v>
@@ -2673,12 +2674,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18">
       <c r="A39" s="2">
-        <v>7496</v>
+        <v>10164</v>
       </c>
       <c r="B39" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2687,7 +2688,7 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -2729,12 +2730,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18">
       <c r="A40" s="2">
-        <v>7499</v>
+        <v>10163</v>
       </c>
       <c r="B40" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2743,7 +2744,7 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
         <v>22</v>
@@ -2785,12 +2786,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18">
       <c r="A41" s="2">
-        <v>7502</v>
+        <v>10162</v>
       </c>
       <c r="B41" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2799,7 +2800,7 @@
         <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
         <v>22</v>
@@ -2841,12 +2842,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18">
       <c r="A42" s="2">
-        <v>7505</v>
+        <v>10160</v>
       </c>
       <c r="B42" s="1">
-        <v>45870</v>
+        <v>46054</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2855,7 +2856,7 @@
         <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
@@ -2894,6 +2895,174 @@
         <v>14</v>
       </c>
       <c r="R42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="2">
+        <v>10159</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" t="s">
+        <v>14</v>
+      </c>
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>14</v>
+      </c>
+      <c r="P43" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>14</v>
+      </c>
+      <c r="R43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="2">
+        <v>10158</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" t="s">
+        <v>14</v>
+      </c>
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>14</v>
+      </c>
+      <c r="P44" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>14</v>
+      </c>
+      <c r="R44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="2">
+        <v>10157</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" t="s">
+        <v>14</v>
+      </c>
+      <c r="M45" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>14</v>
+      </c>
+      <c r="P45" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>14</v>
+      </c>
+      <c r="R45" t="s">
         <v>14</v>
       </c>
     </row>

--- a/selenium_auto/params.xlsx
+++ b/selenium_auto/params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agdy\PycharmProjects\job\selenium_auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8EBBA-578A-4B21-9281-9ED2B1053115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25551593-3474-41C4-B3C1-4FEF388433FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="28800" windowHeight="15370" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
+    <workbookView xWindow="4940" yWindow="4940" windowWidth="19180" windowHeight="8930" xr2:uid="{D0D5463D-061E-4EAD-A0CB-7FEC89F31ECE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="24">
   <si>
     <t>Iot Id</t>
   </si>
@@ -99,16 +99,13 @@
     <t>Датчик зажигания</t>
   </si>
   <si>
+    <t>voltage</t>
+  </si>
+  <si>
     <t>driverIdent</t>
   </si>
   <si>
-    <t>trailer</t>
-  </si>
-  <si>
-    <t>voltage</t>
-  </si>
-  <si>
-    <t>NavTel</t>
+    <t>RFID</t>
   </si>
 </sst>
 </file>
@@ -523,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C7F20B-1701-4DFE-B39C-A4574E6F742B}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -604,22 +601,22 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2">
-        <v>11463</v>
+        <v>7635</v>
       </c>
       <c r="B2" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -628,7 +625,7 @@
         <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -660,22 +657,22 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2">
-        <v>11346</v>
+        <v>8724</v>
       </c>
       <c r="B3" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -684,7 +681,7 @@
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -716,22 +713,22 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2">
-        <v>11345</v>
+        <v>8732</v>
       </c>
       <c r="B4" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
@@ -740,7 +737,7 @@
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -772,22 +769,22 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2">
-        <v>10423</v>
+        <v>8687</v>
       </c>
       <c r="B5" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -796,7 +793,7 @@
         <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -828,22 +825,22 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2">
-        <v>10419</v>
+        <v>6475</v>
       </c>
       <c r="B6" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
@@ -852,7 +849,7 @@
         <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -884,22 +881,22 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2">
-        <v>10418</v>
+        <v>5829</v>
       </c>
       <c r="B7" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -908,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -940,22 +937,22 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2">
-        <v>10416</v>
+        <v>5825</v>
       </c>
       <c r="B8" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -964,7 +961,7 @@
         <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -996,22 +993,22 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2">
-        <v>10415</v>
+        <v>5838</v>
       </c>
       <c r="B9" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
@@ -1020,7 +1017,7 @@
         <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -1052,22 +1049,22 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2">
-        <v>10409</v>
+        <v>5832</v>
       </c>
       <c r="B10" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1076,7 +1073,7 @@
         <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -1108,22 +1105,22 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2">
-        <v>10408</v>
+        <v>5827</v>
       </c>
       <c r="B11" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -1132,7 +1129,7 @@
         <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -1164,22 +1161,22 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2">
-        <v>10407</v>
+        <v>4692</v>
       </c>
       <c r="B12" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -1188,7 +1185,7 @@
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -1220,22 +1217,22 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2">
-        <v>10379</v>
+        <v>4667</v>
       </c>
       <c r="B13" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
@@ -1244,7 +1241,7 @@
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1276,22 +1273,22 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2">
-        <v>10378</v>
+        <v>4664</v>
       </c>
       <c r="B14" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
@@ -1300,7 +1297,7 @@
         <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -1332,22 +1329,22 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2">
-        <v>10377</v>
+        <v>4686</v>
       </c>
       <c r="B15" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
@@ -1356,7 +1353,7 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -1388,22 +1385,22 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2">
-        <v>10376</v>
+        <v>4676</v>
       </c>
       <c r="B16" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
@@ -1412,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -1444,22 +1441,22 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2">
-        <v>10371</v>
+        <v>4665</v>
       </c>
       <c r="B17" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
@@ -1468,7 +1465,7 @@
         <v>20</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -1500,22 +1497,22 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2">
-        <v>10365</v>
+        <v>4682</v>
       </c>
       <c r="B18" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
@@ -1524,7 +1521,7 @@
         <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -1556,22 +1553,22 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2">
-        <v>10364</v>
+        <v>4694</v>
       </c>
       <c r="B19" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
@@ -1580,7 +1577,7 @@
         <v>20</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -1612,22 +1609,22 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2">
-        <v>10363</v>
+        <v>4693</v>
       </c>
       <c r="B20" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
@@ -1636,7 +1633,7 @@
         <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -1668,22 +1665,22 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2">
-        <v>10362</v>
+        <v>5837</v>
       </c>
       <c r="B21" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
@@ -1692,7 +1689,7 @@
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -1724,22 +1721,22 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2">
-        <v>10359</v>
+        <v>4673</v>
       </c>
       <c r="B22" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1748,7 +1745,7 @@
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -1780,22 +1777,22 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2">
-        <v>10180</v>
+        <v>4661</v>
       </c>
       <c r="B23" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
@@ -1804,7 +1801,7 @@
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1836,22 +1833,22 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2">
-        <v>10179</v>
+        <v>4672</v>
       </c>
       <c r="B24" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1860,7 +1857,7 @@
         <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -1892,22 +1889,22 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2">
-        <v>10178</v>
+        <v>4670</v>
       </c>
       <c r="B25" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1916,7 +1913,7 @@
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -1948,22 +1945,22 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2">
-        <v>10177</v>
+        <v>4659</v>
       </c>
       <c r="B26" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
@@ -1972,7 +1969,7 @@
         <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -2004,22 +2001,22 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2">
-        <v>10176</v>
+        <v>5830</v>
       </c>
       <c r="B27" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -2028,7 +2025,7 @@
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -2060,22 +2057,22 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2">
-        <v>10175</v>
+        <v>5834</v>
       </c>
       <c r="B28" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -2084,7 +2081,7 @@
         <v>20</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -2116,22 +2113,22 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2">
-        <v>10174</v>
+        <v>5828</v>
       </c>
       <c r="B29" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -2140,7 +2137,7 @@
         <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2172,22 +2169,22 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2">
-        <v>10173</v>
+        <v>4684</v>
       </c>
       <c r="B30" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -2196,7 +2193,7 @@
         <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2228,22 +2225,22 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2">
-        <v>10172</v>
+        <v>5835</v>
       </c>
       <c r="B31" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
@@ -2252,7 +2249,7 @@
         <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -2284,22 +2281,22 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2">
-        <v>10171</v>
+        <v>4671</v>
       </c>
       <c r="B32" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
@@ -2308,7 +2305,7 @@
         <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -2340,22 +2337,22 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2">
-        <v>10170</v>
+        <v>4669</v>
       </c>
       <c r="B33" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
@@ -2364,7 +2361,7 @@
         <v>20</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2396,22 +2393,22 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2">
-        <v>10169</v>
+        <v>4685</v>
       </c>
       <c r="B34" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
@@ -2420,7 +2417,7 @@
         <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2452,22 +2449,22 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2">
-        <v>10168</v>
+        <v>4679</v>
       </c>
       <c r="B35" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -2476,7 +2473,7 @@
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2508,22 +2505,22 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2">
-        <v>10167</v>
+        <v>4674</v>
       </c>
       <c r="B36" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
@@ -2532,7 +2529,7 @@
         <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -2564,22 +2561,22 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="2">
-        <v>10166</v>
+        <v>4691</v>
       </c>
       <c r="B37" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -2588,7 +2585,7 @@
         <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2620,22 +2617,22 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="2">
-        <v>10165</v>
+        <v>7718</v>
       </c>
       <c r="B38" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
@@ -2644,7 +2641,7 @@
         <v>20</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -2676,22 +2673,22 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="2">
-        <v>10164</v>
+        <v>11111</v>
       </c>
       <c r="B39" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -2700,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -2732,22 +2729,22 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="2">
-        <v>10163</v>
+        <v>4690</v>
       </c>
       <c r="B40" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
@@ -2756,7 +2753,7 @@
         <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -2788,22 +2785,22 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="2">
-        <v>10162</v>
+        <v>5836</v>
       </c>
       <c r="B41" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -2812,7 +2809,7 @@
         <v>20</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -2844,22 +2841,22 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="2">
-        <v>10160</v>
+        <v>4678</v>
       </c>
       <c r="B42" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s">
         <v>14</v>
@@ -2868,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -2900,22 +2897,22 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="2">
-        <v>10159</v>
+        <v>4852</v>
       </c>
       <c r="B43" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
@@ -2924,7 +2921,7 @@
         <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2956,22 +2953,22 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="2">
-        <v>10158</v>
+        <v>5831</v>
       </c>
       <c r="B44" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
@@ -2980,7 +2977,7 @@
         <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -3012,22 +3009,22 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="2">
-        <v>10157</v>
+        <v>4668</v>
       </c>
       <c r="B45" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
@@ -3036,7 +3033,7 @@
         <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -3063,6 +3060,174 @@
         <v>14</v>
       </c>
       <c r="R45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="2">
+        <v>4660</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" t="s">
+        <v>14</v>
+      </c>
+      <c r="M46" t="s">
+        <v>14</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>14</v>
+      </c>
+      <c r="P46" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>14</v>
+      </c>
+      <c r="R46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="2">
+        <v>4663</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" t="s">
+        <v>14</v>
+      </c>
+      <c r="M47" t="s">
+        <v>14</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>14</v>
+      </c>
+      <c r="P47" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>14</v>
+      </c>
+      <c r="R47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="2">
+        <v>4688</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" t="s">
+        <v>14</v>
+      </c>
+      <c r="M48" t="s">
+        <v>14</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>14</v>
+      </c>
+      <c r="P48" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>14</v>
+      </c>
+      <c r="R48" t="s">
         <v>14</v>
       </c>
     </row>
